--- a/Team-Data/2010-11/3-27-2010-11.xlsx
+++ b/Team-Data/2010-11/3-27-2010-11.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -676,52 +743,52 @@
         <v>48.1</v>
       </c>
       <c r="I2" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J2" t="n">
-        <v>78.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K2" t="n">
         <v>0.462</v>
       </c>
       <c r="L2" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="M2" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="N2" t="n">
-        <v>0.352</v>
+        <v>0.354</v>
       </c>
       <c r="O2" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="P2" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.776</v>
+        <v>0.778</v>
       </c>
       <c r="R2" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="S2" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="T2" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="U2" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="V2" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="W2" t="n">
         <v>6.1</v>
       </c>
       <c r="X2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y2" t="n">
         <v>4.3</v>
@@ -733,22 +800,22 @@
         <v>18.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>95.09999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="AC2" t="n">
         <v>-0.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AF2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
         <v>28</v>
@@ -760,7 +827,7 @@
         <v>24</v>
       </c>
       <c r="AK2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL2" t="n">
         <v>13</v>
@@ -769,7 +836,7 @@
         <v>16</v>
       </c>
       <c r="AN2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AO2" t="n">
         <v>29</v>
@@ -778,13 +845,13 @@
         <v>30</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT2" t="n">
         <v>26</v>
@@ -793,7 +860,7 @@
         <v>9</v>
       </c>
       <c r="AV2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW2" t="n">
         <v>29</v>
@@ -802,7 +869,7 @@
         <v>28</v>
       </c>
       <c r="AY2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ2" t="n">
         <v>3</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-27-2010-11</t>
+          <t>2011-03-27</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E3" t="n">
         <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" t="n">
-        <v>0.714</v>
+        <v>0.704</v>
       </c>
       <c r="H3" t="n">
         <v>48.2</v>
@@ -861,43 +928,43 @@
         <v>37</v>
       </c>
       <c r="J3" t="n">
-        <v>76.3</v>
+        <v>76.2</v>
       </c>
       <c r="K3" t="n">
-        <v>0.485</v>
+        <v>0.486</v>
       </c>
       <c r="L3" t="n">
         <v>5.1</v>
       </c>
       <c r="M3" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.363</v>
+        <v>0.366</v>
       </c>
       <c r="O3" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="P3" t="n">
         <v>23.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.77</v>
+        <v>0.767</v>
       </c>
       <c r="R3" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="S3" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="T3" t="n">
         <v>39</v>
       </c>
       <c r="U3" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="V3" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="W3" t="n">
         <v>8.4</v>
@@ -906,37 +973,37 @@
         <v>4.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z3" t="n">
         <v>20.8</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AB3" t="n">
-        <v>96.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="AD3" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AE3" t="n">
         <v>5</v>
       </c>
       <c r="AF3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH3" t="n">
         <v>23</v>
       </c>
       <c r="AI3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -951,16 +1018,16 @@
         <v>28</v>
       </c>
       <c r="AN3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP3" t="n">
         <v>24</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AR3" t="n">
         <v>30</v>
@@ -972,31 +1039,31 @@
         <v>29</v>
       </c>
       <c r="AU3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AW3" t="n">
         <v>3</v>
       </c>
       <c r="AX3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ3" t="n">
         <v>16</v>
       </c>
       <c r="BA3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB3" t="n">
         <v>21</v>
       </c>
       <c r="BC3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-27-2010-11</t>
+          <t>2011-03-27</t>
         </is>
       </c>
     </row>
@@ -1025,25 +1092,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E4" t="n">
         <v>30</v>
       </c>
       <c r="F4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>0.423</v>
+        <v>0.417</v>
       </c>
       <c r="H4" t="n">
         <v>48.3</v>
       </c>
       <c r="I4" t="n">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="J4" t="n">
-        <v>77.59999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="K4" t="n">
         <v>0.447</v>
@@ -1055,7 +1122,7 @@
         <v>15.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.325</v>
+        <v>0.326</v>
       </c>
       <c r="O4" t="n">
         <v>18.9</v>
@@ -1064,22 +1131,22 @@
         <v>25</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.754</v>
+        <v>0.757</v>
       </c>
       <c r="R4" t="n">
         <v>10.7</v>
       </c>
       <c r="S4" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="T4" t="n">
-        <v>41</v>
+        <v>40.9</v>
       </c>
       <c r="U4" t="n">
         <v>20.4</v>
       </c>
       <c r="V4" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W4" t="n">
         <v>6.4</v>
@@ -1094,16 +1161,16 @@
         <v>20.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>93.2</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>-3.8</v>
+        <v>-4</v>
       </c>
       <c r="AD4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AE4" t="n">
         <v>21</v>
@@ -1124,7 +1191,7 @@
         <v>28</v>
       </c>
       <c r="AK4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL4" t="n">
         <v>28</v>
@@ -1142,7 +1209,7 @@
         <v>10</v>
       </c>
       <c r="AQ4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AR4" t="n">
         <v>18</v>
@@ -1151,13 +1218,13 @@
         <v>20</v>
       </c>
       <c r="AT4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW4" t="n">
         <v>28</v>
@@ -1166,10 +1233,10 @@
         <v>7</v>
       </c>
       <c r="AY4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AZ4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA4" t="n">
         <v>9</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-27-2010-11</t>
+          <t>2011-03-27</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E5" t="n">
         <v>53</v>
       </c>
       <c r="F5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G5" t="n">
-        <v>0.746</v>
+        <v>0.736</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
@@ -1225,19 +1292,19 @@
         <v>37.1</v>
       </c>
       <c r="J5" t="n">
-        <v>80.5</v>
+        <v>80.7</v>
       </c>
       <c r="K5" t="n">
         <v>0.46</v>
       </c>
       <c r="L5" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="M5" t="n">
         <v>17.3</v>
       </c>
       <c r="N5" t="n">
-        <v>0.363</v>
+        <v>0.361</v>
       </c>
       <c r="O5" t="n">
         <v>18.1</v>
@@ -1246,7 +1313,7 @@
         <v>24.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.736</v>
+        <v>0.734</v>
       </c>
       <c r="R5" t="n">
         <v>12</v>
@@ -1255,7 +1322,7 @@
         <v>32.3</v>
       </c>
       <c r="T5" t="n">
-        <v>44.3</v>
+        <v>44.4</v>
       </c>
       <c r="U5" t="n">
         <v>21.9</v>
@@ -1264,16 +1331,16 @@
         <v>14.1</v>
       </c>
       <c r="W5" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X5" t="n">
         <v>5.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z5" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA5" t="n">
         <v>20.4</v>
@@ -1282,10 +1349,10 @@
         <v>98.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AE5" t="n">
         <v>2</v>
@@ -1300,25 +1367,25 @@
         <v>10</v>
       </c>
       <c r="AI5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>17</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>18</v>
       </c>
       <c r="AK5" t="n">
         <v>16</v>
       </c>
       <c r="AL5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM5" t="n">
         <v>17</v>
       </c>
       <c r="AN5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AO5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP5" t="n">
         <v>12</v>
@@ -1327,7 +1394,7 @@
         <v>26</v>
       </c>
       <c r="AR5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS5" t="n">
         <v>4</v>
@@ -1339,7 +1406,7 @@
         <v>14</v>
       </c>
       <c r="AV5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW5" t="n">
         <v>20</v>
@@ -1351,10 +1418,10 @@
         <v>26</v>
       </c>
       <c r="AZ5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB5" t="n">
         <v>20</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-27-2010-11</t>
+          <t>2011-03-27</t>
         </is>
       </c>
     </row>
@@ -1392,25 +1459,25 @@
         <v>71</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G6" t="n">
-        <v>0.183</v>
+        <v>0.197</v>
       </c>
       <c r="H6" t="n">
         <v>48.2</v>
       </c>
       <c r="I6" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="J6" t="n">
-        <v>81.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.428</v>
+        <v>0.43</v>
       </c>
       <c r="L6" t="n">
         <v>6.2</v>
@@ -1419,34 +1486,34 @@
         <v>18.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="O6" t="n">
         <v>18.7</v>
       </c>
       <c r="P6" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.742</v>
+        <v>0.744</v>
       </c>
       <c r="R6" t="n">
         <v>10.6</v>
       </c>
       <c r="S6" t="n">
-        <v>30</v>
+        <v>29.8</v>
       </c>
       <c r="T6" t="n">
-        <v>40.6</v>
+        <v>40.5</v>
       </c>
       <c r="U6" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V6" t="n">
         <v>14.4</v>
       </c>
       <c r="W6" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="X6" t="n">
         <v>4.1</v>
@@ -1455,19 +1522,19 @@
         <v>6</v>
       </c>
       <c r="Z6" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AA6" t="n">
         <v>21.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>94.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>-10.6</v>
+        <v>-10.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AE6" t="n">
         <v>30</v>
@@ -1479,7 +1546,7 @@
         <v>30</v>
       </c>
       <c r="AH6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI6" t="n">
         <v>28</v>
@@ -1491,10 +1558,10 @@
         <v>29</v>
       </c>
       <c r="AL6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AM6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN6" t="n">
         <v>23</v>
@@ -1503,7 +1570,7 @@
         <v>12</v>
       </c>
       <c r="AP6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ6" t="n">
         <v>25</v>
@@ -1515,10 +1582,10 @@
         <v>23</v>
       </c>
       <c r="AT6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AU6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AV6" t="n">
         <v>20</v>
@@ -1536,7 +1603,7 @@
         <v>8</v>
       </c>
       <c r="BA6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB6" t="n">
         <v>27</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-27-2010-11</t>
+          <t>2011-03-27</t>
         </is>
       </c>
     </row>
@@ -1586,91 +1653,91 @@
         <v>48</v>
       </c>
       <c r="I7" t="n">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="J7" t="n">
-        <v>78.5</v>
+        <v>78.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0.475</v>
+        <v>0.477</v>
       </c>
       <c r="L7" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M7" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="N7" t="n">
-        <v>0.371</v>
+        <v>0.37</v>
       </c>
       <c r="O7" t="n">
         <v>17.6</v>
       </c>
       <c r="P7" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="Q7" t="n">
         <v>0.785</v>
       </c>
       <c r="R7" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S7" t="n">
         <v>31.9</v>
       </c>
       <c r="T7" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="U7" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="V7" t="n">
         <v>13.8</v>
       </c>
       <c r="W7" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="X7" t="n">
         <v>4.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Z7" t="n">
         <v>19.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AB7" t="n">
-        <v>100.1</v>
+        <v>100.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AE7" t="n">
         <v>4</v>
       </c>
       <c r="AF7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH7" t="n">
         <v>30</v>
       </c>
       <c r="AI7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ7" t="n">
         <v>26</v>
       </c>
       <c r="AK7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL7" t="n">
         <v>8</v>
@@ -1682,7 +1749,7 @@
         <v>7</v>
       </c>
       <c r="AO7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP7" t="n">
         <v>26</v>
@@ -1691,25 +1758,25 @@
         <v>5</v>
       </c>
       <c r="AR7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
         <v>15</v>
       </c>
       <c r="AU7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV7" t="n">
         <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AY7" t="n">
         <v>2</v>
@@ -1721,7 +1788,7 @@
         <v>25</v>
       </c>
       <c r="BB7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC7" t="n">
         <v>8</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-27-2010-11</t>
+          <t>2011-03-27</t>
         </is>
       </c>
     </row>
@@ -1753,28 +1820,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E8" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F8" t="n">
         <v>29</v>
       </c>
       <c r="G8" t="n">
-        <v>0.597</v>
+        <v>0.603</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
       </c>
       <c r="I8" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="J8" t="n">
         <v>80.40000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.476</v>
+        <v>0.475</v>
       </c>
       <c r="L8" t="n">
         <v>8.199999999999999</v>
@@ -1783,19 +1850,19 @@
         <v>20.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0.392</v>
+        <v>0.391</v>
       </c>
       <c r="O8" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="P8" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.773</v>
+        <v>0.774</v>
       </c>
       <c r="R8" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="S8" t="n">
         <v>32.3</v>
@@ -1819,19 +1886,19 @@
         <v>6</v>
       </c>
       <c r="Z8" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>107.6</v>
+        <v>107.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1846,13 +1913,13 @@
         <v>29</v>
       </c>
       <c r="AI8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AJ8" t="n">
         <v>22</v>
       </c>
       <c r="AK8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL8" t="n">
         <v>7</v>
@@ -1873,7 +1940,7 @@
         <v>10</v>
       </c>
       <c r="AR8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS8" t="n">
         <v>5</v>
@@ -1888,10 +1955,10 @@
         <v>15</v>
       </c>
       <c r="AW8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY8" t="n">
         <v>28</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-27-2010-11</t>
+          <t>2011-03-27</t>
         </is>
       </c>
     </row>
@@ -1935,19 +2002,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E9" t="n">
         <v>26</v>
       </c>
       <c r="F9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G9" t="n">
-        <v>0.361</v>
+        <v>0.356</v>
       </c>
       <c r="H9" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I9" t="n">
         <v>36.9</v>
@@ -1962,7 +2029,7 @@
         <v>5.9</v>
       </c>
       <c r="M9" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="N9" t="n">
         <v>0.381</v>
@@ -1971,10 +2038,10 @@
         <v>16.3</v>
       </c>
       <c r="P9" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.733</v>
+        <v>0.729</v>
       </c>
       <c r="R9" t="n">
         <v>11.3</v>
@@ -1983,13 +2050,13 @@
         <v>27</v>
       </c>
       <c r="T9" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="U9" t="n">
         <v>20.9</v>
       </c>
       <c r="V9" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="W9" t="n">
         <v>7.2</v>
@@ -2013,7 +2080,7 @@
         <v>-4</v>
       </c>
       <c r="AD9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AE9" t="n">
         <v>24</v>
@@ -2028,7 +2095,7 @@
         <v>6</v>
       </c>
       <c r="AI9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AJ9" t="n">
         <v>14</v>
@@ -2037,28 +2104,28 @@
         <v>20</v>
       </c>
       <c r="AL9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM9" t="n">
         <v>21</v>
       </c>
       <c r="AN9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO9" t="n">
         <v>28</v>
       </c>
       <c r="AP9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>28</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>27</v>
       </c>
       <c r="AR9" t="n">
         <v>12</v>
       </c>
       <c r="AS9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT9" t="n">
         <v>30</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-27-2010-11</t>
+          <t>2011-03-27</t>
         </is>
       </c>
     </row>
@@ -2132,34 +2199,34 @@
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>39.4</v>
+        <v>39.5</v>
       </c>
       <c r="J10" t="n">
         <v>85.40000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.462</v>
+        <v>0.463</v>
       </c>
       <c r="L10" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M10" t="n">
         <v>21.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0.394</v>
+        <v>0.393</v>
       </c>
       <c r="O10" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="P10" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.754</v>
+        <v>0.757</v>
       </c>
       <c r="R10" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S10" t="n">
         <v>28.7</v>
@@ -2180,28 +2247,28 @@
         <v>4.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA10" t="n">
         <v>18.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>102.9</v>
+        <v>103.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.9</v>
+        <v>-3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE10" t="n">
         <v>20</v>
       </c>
       <c r="AF10" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG10" t="n">
         <v>20</v>
@@ -2216,7 +2283,7 @@
         <v>2</v>
       </c>
       <c r="AK10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL10" t="n">
         <v>5</v>
@@ -2234,10 +2301,10 @@
         <v>29</v>
       </c>
       <c r="AQ10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AS10" t="n">
         <v>26</v>
@@ -2249,7 +2316,7 @@
         <v>8</v>
       </c>
       <c r="AV10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW10" t="n">
         <v>2</v>
@@ -2258,10 +2325,10 @@
         <v>15</v>
       </c>
       <c r="AY10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BA10" t="n">
         <v>29</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-27-2010-11</t>
+          <t>2011-03-27</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E11" t="n">
         <v>38</v>
       </c>
       <c r="F11" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G11" t="n">
-        <v>0.535</v>
+        <v>0.528</v>
       </c>
       <c r="H11" t="n">
         <v>48.4</v>
@@ -2317,46 +2384,46 @@
         <v>38.5</v>
       </c>
       <c r="J11" t="n">
-        <v>84.7</v>
+        <v>84.8</v>
       </c>
       <c r="K11" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L11" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0.368</v>
+        <v>0.367</v>
       </c>
       <c r="O11" t="n">
-        <v>20.3</v>
+        <v>20.6</v>
       </c>
       <c r="P11" t="n">
-        <v>25.5</v>
+        <v>25.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.795</v>
+        <v>0.797</v>
       </c>
       <c r="R11" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S11" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T11" t="n">
-        <v>42.3</v>
+        <v>42.6</v>
       </c>
       <c r="U11" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="V11" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="W11" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X11" t="n">
         <v>4.7</v>
@@ -2365,19 +2432,19 @@
         <v>5.7</v>
       </c>
       <c r="Z11" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>105.6</v>
+        <v>105.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AE11" t="n">
         <v>14</v>
@@ -2407,52 +2474,52 @@
         <v>4</v>
       </c>
       <c r="AN11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP11" t="n">
         <v>5</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>6</v>
       </c>
       <c r="AQ11" t="n">
         <v>4</v>
       </c>
       <c r="AR11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AS11" t="n">
         <v>13</v>
       </c>
       <c r="AT11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV11" t="n">
         <v>6</v>
       </c>
       <c r="AW11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX11" t="n">
         <v>18</v>
       </c>
       <c r="AY11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ11" t="n">
         <v>12</v>
       </c>
       <c r="BA11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB11" t="n">
         <v>3</v>
       </c>
       <c r="BC11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-27-2010-11</t>
+          <t>2011-03-27</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E12" t="n">
         <v>32</v>
       </c>
       <c r="F12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G12" t="n">
-        <v>0.438</v>
+        <v>0.432</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
@@ -2499,10 +2566,10 @@
         <v>36.3</v>
       </c>
       <c r="J12" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="K12" t="n">
-        <v>0.438</v>
+        <v>0.439</v>
       </c>
       <c r="L12" t="n">
         <v>7.2</v>
@@ -2514,13 +2581,13 @@
         <v>0.353</v>
       </c>
       <c r="O12" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="P12" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.784</v>
+        <v>0.782</v>
       </c>
       <c r="R12" t="n">
         <v>11.2</v>
@@ -2529,13 +2596,13 @@
         <v>32.7</v>
       </c>
       <c r="T12" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="U12" t="n">
         <v>19.5</v>
       </c>
       <c r="V12" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W12" t="n">
         <v>7.1</v>
@@ -2547,16 +2614,16 @@
         <v>5.9</v>
       </c>
       <c r="Z12" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AA12" t="n">
         <v>21.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>99.2</v>
+        <v>99.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>-1.3</v>
+        <v>-1.5</v>
       </c>
       <c r="AD12" t="n">
         <v>1</v>
@@ -2577,7 +2644,7 @@
         <v>23</v>
       </c>
       <c r="AJ12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK12" t="n">
         <v>26</v>
@@ -2589,7 +2656,7 @@
         <v>9</v>
       </c>
       <c r="AN12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO12" t="n">
         <v>7</v>
@@ -2598,7 +2665,7 @@
         <v>11</v>
       </c>
       <c r="AQ12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR12" t="n">
         <v>14</v>
@@ -2613,7 +2680,7 @@
         <v>29</v>
       </c>
       <c r="AV12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW12" t="n">
         <v>21</v>
@@ -2628,13 +2695,13 @@
         <v>22</v>
       </c>
       <c r="BA12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BC12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-27-2010-11</t>
+          <t>2011-03-27</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E13" t="n">
         <v>29</v>
       </c>
       <c r="F13" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G13" t="n">
-        <v>0.397</v>
+        <v>0.392</v>
       </c>
       <c r="H13" t="n">
         <v>48.5</v>
@@ -2684,7 +2751,7 @@
         <v>80.40000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L13" t="n">
         <v>6.3</v>
@@ -2693,31 +2760,31 @@
         <v>18.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0.339</v>
+        <v>0.338</v>
       </c>
       <c r="O13" t="n">
         <v>19</v>
       </c>
       <c r="P13" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.71</v>
+        <v>0.709</v>
       </c>
       <c r="R13" t="n">
         <v>11.6</v>
       </c>
       <c r="S13" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T13" t="n">
         <v>42</v>
       </c>
       <c r="U13" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V13" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="W13" t="n">
         <v>6.9</v>
@@ -2735,10 +2802,10 @@
         <v>22.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>99.09999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>-2.8</v>
+        <v>-2.9</v>
       </c>
       <c r="AD13" t="n">
         <v>1</v>
@@ -2753,19 +2820,19 @@
         <v>23</v>
       </c>
       <c r="AH13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK13" t="n">
         <v>18</v>
       </c>
       <c r="AL13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AM13" t="n">
         <v>11</v>
@@ -2804,13 +2871,13 @@
         <v>13</v>
       </c>
       <c r="AY13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AZ13" t="n">
         <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB13" t="n">
         <v>18</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-27-2010-11</t>
+          <t>2011-03-27</t>
         </is>
       </c>
     </row>
@@ -2863,25 +2930,25 @@
         <v>38.4</v>
       </c>
       <c r="J14" t="n">
-        <v>82.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.466</v>
+        <v>0.465</v>
       </c>
       <c r="L14" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="M14" t="n">
         <v>18.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0.354</v>
+        <v>0.357</v>
       </c>
       <c r="O14" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P14" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="Q14" t="n">
         <v>0.783</v>
@@ -2899,7 +2966,7 @@
         <v>22.1</v>
       </c>
       <c r="V14" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="W14" t="n">
         <v>7.4</v>
@@ -2917,13 +2984,13 @@
         <v>20.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>101.8</v>
+        <v>102</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2935,13 +3002,13 @@
         <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI14" t="n">
         <v>6</v>
       </c>
       <c r="AJ14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK14" t="n">
         <v>9</v>
@@ -2950,7 +3017,7 @@
         <v>12</v>
       </c>
       <c r="AM14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN14" t="n">
         <v>16</v>
@@ -2962,10 +3029,10 @@
         <v>17</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS14" t="n">
         <v>9</v>
@@ -2980,13 +3047,13 @@
         <v>2</v>
       </c>
       <c r="AW14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AX14" t="n">
         <v>11</v>
       </c>
       <c r="AY14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ14" t="n">
         <v>2</v>
@@ -2995,7 +3062,7 @@
         <v>19</v>
       </c>
       <c r="BB14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC14" t="n">
         <v>3</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-27-2010-11</t>
+          <t>2011-03-27</t>
         </is>
       </c>
     </row>
@@ -3030,31 +3097,31 @@
         <v>73</v>
       </c>
       <c r="E15" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.548</v>
       </c>
       <c r="H15" t="n">
         <v>48.5</v>
       </c>
       <c r="I15" t="n">
-        <v>39</v>
+        <v>38.9</v>
       </c>
       <c r="J15" t="n">
-        <v>83.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="K15" t="n">
-        <v>0.469</v>
+        <v>0.468</v>
       </c>
       <c r="L15" t="n">
         <v>3.7</v>
       </c>
       <c r="M15" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="N15" t="n">
         <v>0.326</v>
@@ -3063,10 +3130,10 @@
         <v>18.3</v>
       </c>
       <c r="P15" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.754</v>
+        <v>0.755</v>
       </c>
       <c r="R15" t="n">
         <v>11.8</v>
@@ -3075,10 +3142,10 @@
         <v>29.1</v>
       </c>
       <c r="T15" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="U15" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V15" t="n">
         <v>13.9</v>
@@ -3093,31 +3160,31 @@
         <v>6.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AA15" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AF15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AG15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI15" t="n">
         <v>3</v>
@@ -3144,7 +3211,7 @@
         <v>14</v>
       </c>
       <c r="AQ15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR15" t="n">
         <v>7</v>
@@ -3153,34 +3220,34 @@
         <v>24</v>
       </c>
       <c r="AT15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU15" t="n">
         <v>20</v>
       </c>
       <c r="AV15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW15" t="n">
         <v>1</v>
       </c>
       <c r="AX15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AZ15" t="n">
         <v>18</v>
       </c>
       <c r="BA15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BB15" t="n">
         <v>13</v>
       </c>
       <c r="BC15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-27-2010-11</t>
+          <t>2011-03-27</t>
         </is>
       </c>
     </row>
@@ -3209,28 +3276,28 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E16" t="n">
         <v>50</v>
       </c>
       <c r="F16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G16" t="n">
-        <v>0.704</v>
+        <v>0.694</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>37.1</v>
+        <v>36.8</v>
       </c>
       <c r="J16" t="n">
-        <v>77.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.48</v>
+        <v>0.478</v>
       </c>
       <c r="L16" t="n">
         <v>6.6</v>
@@ -3239,34 +3306,34 @@
         <v>18</v>
       </c>
       <c r="N16" t="n">
-        <v>0.365</v>
+        <v>0.368</v>
       </c>
       <c r="O16" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="P16" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.772</v>
+        <v>0.77</v>
       </c>
       <c r="R16" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="S16" t="n">
-        <v>32.9</v>
+        <v>32.8</v>
       </c>
       <c r="T16" t="n">
-        <v>42.6</v>
+        <v>42.4</v>
       </c>
       <c r="U16" t="n">
         <v>19.7</v>
       </c>
       <c r="V16" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="W16" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="X16" t="n">
         <v>5.4</v>
@@ -3281,19 +3348,19 @@
         <v>21.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>102.4</v>
+        <v>101.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AE16" t="n">
         <v>5</v>
       </c>
       <c r="AF16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG16" t="n">
         <v>6</v>
@@ -3302,7 +3369,7 @@
         <v>17</v>
       </c>
       <c r="AI16" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AJ16" t="n">
         <v>29</v>
@@ -3317,7 +3384,7 @@
         <v>15</v>
       </c>
       <c r="AN16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO16" t="n">
         <v>3</v>
@@ -3326,28 +3393,28 @@
         <v>3</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AR16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU16" t="n">
         <v>28</v>
       </c>
       <c r="AV16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY16" t="n">
         <v>1</v>
@@ -3359,7 +3426,7 @@
         <v>5</v>
       </c>
       <c r="BB16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC16" t="n">
         <v>2</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-27-2010-11</t>
+          <t>2011-03-27</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E17" t="n">
         <v>29</v>
       </c>
       <c r="F17" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G17" t="n">
-        <v>0.408</v>
+        <v>0.403</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3418,7 +3485,7 @@
         <v>5.9</v>
       </c>
       <c r="M17" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="N17" t="n">
         <v>0.346</v>
@@ -3427,19 +3494,19 @@
         <v>17.4</v>
       </c>
       <c r="P17" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.753</v>
+        <v>0.75</v>
       </c>
       <c r="R17" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S17" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="T17" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="U17" t="n">
         <v>18.7</v>
@@ -3451,16 +3518,16 @@
         <v>7.4</v>
       </c>
       <c r="X17" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z17" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB17" t="n">
         <v>91.5</v>
@@ -3469,13 +3536,13 @@
         <v>-1.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AE17" t="n">
         <v>22</v>
       </c>
       <c r="AF17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG17" t="n">
         <v>22</v>
@@ -3493,13 +3560,13 @@
         <v>30</v>
       </c>
       <c r="AL17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM17" t="n">
         <v>18</v>
       </c>
       <c r="AN17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO17" t="n">
         <v>27</v>
@@ -3514,7 +3581,7 @@
         <v>17</v>
       </c>
       <c r="AS17" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AT17" t="n">
         <v>16</v>
@@ -3526,13 +3593,13 @@
         <v>7</v>
       </c>
       <c r="AW17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX17" t="n">
         <v>12</v>
       </c>
       <c r="AY17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ17" t="n">
         <v>15</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-27-2010-11</t>
+          <t>2011-03-27</t>
         </is>
       </c>
     </row>
@@ -3588,13 +3655,13 @@
         <v>48.2</v>
       </c>
       <c r="I18" t="n">
-        <v>37.5</v>
+        <v>37.6</v>
       </c>
       <c r="J18" t="n">
-        <v>85.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="K18" t="n">
-        <v>0.438</v>
+        <v>0.439</v>
       </c>
       <c r="L18" t="n">
         <v>7.2</v>
@@ -3606,25 +3673,25 @@
         <v>0.375</v>
       </c>
       <c r="O18" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P18" t="n">
         <v>24.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.767</v>
+        <v>0.768</v>
       </c>
       <c r="R18" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="S18" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="T18" t="n">
         <v>45</v>
       </c>
       <c r="U18" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V18" t="n">
         <v>17.2</v>
@@ -3639,19 +3706,19 @@
         <v>5.8</v>
       </c>
       <c r="Z18" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>100.8</v>
+        <v>101.3</v>
       </c>
       <c r="AC18" t="n">
         <v>-5.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE18" t="n">
         <v>28</v>
@@ -3663,10 +3730,10 @@
         <v>29</v>
       </c>
       <c r="AH18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ18" t="n">
         <v>1</v>
@@ -3690,7 +3757,7 @@
         <v>13</v>
       </c>
       <c r="AQ18" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AR18" t="n">
         <v>1</v>
@@ -3708,7 +3775,7 @@
         <v>30</v>
       </c>
       <c r="AW18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX18" t="n">
         <v>10</v>
@@ -3720,7 +3787,7 @@
         <v>28</v>
       </c>
       <c r="BA18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-27-2010-11</t>
+          <t>2011-03-27</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F19" t="n">
         <v>49</v>
       </c>
       <c r="G19" t="n">
-        <v>0.31</v>
+        <v>0.319</v>
       </c>
       <c r="H19" t="n">
         <v>48.9</v>
@@ -3776,16 +3843,16 @@
         <v>80.5</v>
       </c>
       <c r="K19" t="n">
-        <v>0.437</v>
+        <v>0.438</v>
       </c>
       <c r="L19" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="M19" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0.341</v>
+        <v>0.342</v>
       </c>
       <c r="O19" t="n">
         <v>17.6</v>
@@ -3800,13 +3867,13 @@
         <v>11.2</v>
       </c>
       <c r="S19" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="T19" t="n">
         <v>41.5</v>
       </c>
       <c r="U19" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V19" t="n">
         <v>14.4</v>
@@ -3827,13 +3894,13 @@
         <v>20.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>93.5</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>-5.7</v>
+        <v>-5.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AE19" t="n">
         <v>25</v>
@@ -3863,13 +3930,13 @@
         <v>20</v>
       </c>
       <c r="AN19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ19" t="n">
         <v>18</v>
@@ -3878,16 +3945,16 @@
         <v>13</v>
       </c>
       <c r="AS19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT19" t="n">
         <v>14</v>
       </c>
       <c r="AU19" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AV19" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AW19" t="n">
         <v>30</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-27-2010-11</t>
+          <t>2011-03-27</t>
         </is>
       </c>
     </row>
@@ -3940,13 +4007,13 @@
         <v>73</v>
       </c>
       <c r="E20" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F20" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.575</v>
       </c>
       <c r="H20" t="n">
         <v>48.4</v>
@@ -3955,10 +4022,10 @@
         <v>36</v>
       </c>
       <c r="J20" t="n">
-        <v>78.3</v>
+        <v>78.2</v>
       </c>
       <c r="K20" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="L20" t="n">
         <v>5.4</v>
@@ -3967,22 +4034,22 @@
         <v>15.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.357</v>
+        <v>0.358</v>
       </c>
       <c r="O20" t="n">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="P20" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.767</v>
+        <v>0.768</v>
       </c>
       <c r="R20" t="n">
-        <v>10.1</v>
+        <v>9.9</v>
       </c>
       <c r="S20" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="T20" t="n">
         <v>40.5</v>
@@ -3997,25 +4064,25 @@
         <v>7.5</v>
       </c>
       <c r="X20" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AA20" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>95.09999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE20" t="n">
         <v>10</v>
@@ -4027,7 +4094,7 @@
         <v>11</v>
       </c>
       <c r="AH20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI20" t="n">
         <v>26</v>
@@ -4042,25 +4109,25 @@
         <v>23</v>
       </c>
       <c r="AM20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AN20" t="n">
         <v>15</v>
       </c>
       <c r="AO20" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AP20" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AQ20" t="n">
         <v>15</v>
       </c>
       <c r="AR20" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AS20" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AT20" t="n">
         <v>21</v>
@@ -4069,10 +4136,10 @@
         <v>21</v>
       </c>
       <c r="AV20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX20" t="n">
         <v>20</v>
@@ -4084,13 +4151,13 @@
         <v>17</v>
       </c>
       <c r="BA20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BB20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-27-2010-11</t>
+          <t>2011-03-27</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E21" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F21" t="n">
         <v>38</v>
       </c>
       <c r="G21" t="n">
-        <v>0.472</v>
+        <v>0.479</v>
       </c>
       <c r="H21" t="n">
         <v>48.2</v>
@@ -4137,7 +4204,7 @@
         <v>38.2</v>
       </c>
       <c r="J21" t="n">
-        <v>83.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="K21" t="n">
         <v>0.457</v>
@@ -4149,37 +4216,37 @@
         <v>24.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="O21" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="P21" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="R21" t="n">
         <v>10.4</v>
       </c>
       <c r="S21" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T21" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="U21" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V21" t="n">
         <v>13.9</v>
       </c>
       <c r="W21" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X21" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Y21" t="n">
         <v>4.5</v>
@@ -4191,25 +4258,25 @@
         <v>20.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>106</v>
+        <v>105.9</v>
       </c>
       <c r="AC21" t="n">
         <v>0.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AE21" t="n">
         <v>18</v>
       </c>
       <c r="AF21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG21" t="n">
         <v>18</v>
       </c>
       <c r="AH21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI21" t="n">
         <v>8</v>
@@ -4230,10 +4297,10 @@
         <v>8</v>
       </c>
       <c r="AO21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ21" t="n">
         <v>2</v>
@@ -4242,22 +4309,22 @@
         <v>22</v>
       </c>
       <c r="AS21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT21" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AU21" t="n">
         <v>15</v>
       </c>
       <c r="AV21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW21" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY21" t="n">
         <v>12</v>
@@ -4266,7 +4333,7 @@
         <v>21</v>
       </c>
       <c r="BA21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB21" t="n">
         <v>2</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-27-2010-11</t>
+          <t>2011-03-27</t>
         </is>
       </c>
     </row>
@@ -4325,61 +4392,61 @@
         <v>0.463</v>
       </c>
       <c r="L22" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="M22" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="N22" t="n">
-        <v>0.352</v>
+        <v>0.349</v>
       </c>
       <c r="O22" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="P22" t="n">
-        <v>29</v>
+        <v>29.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.824</v>
+        <v>0.823</v>
       </c>
       <c r="R22" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S22" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T22" t="n">
         <v>42.3</v>
       </c>
       <c r="U22" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V22" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="W22" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X22" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Y22" t="n">
         <v>4.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>104.4</v>
+        <v>104.5</v>
       </c>
       <c r="AC22" t="n">
         <v>3.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AE22" t="n">
         <v>7</v>
@@ -4394,22 +4461,22 @@
         <v>3</v>
       </c>
       <c r="AI22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ22" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AK22" t="n">
         <v>11</v>
       </c>
       <c r="AL22" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AM22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO22" t="n">
         <v>1</v>
@@ -4421,7 +4488,7 @@
         <v>1</v>
       </c>
       <c r="AR22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS22" t="n">
         <v>10</v>
@@ -4430,7 +4497,7 @@
         <v>9</v>
       </c>
       <c r="AU22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV22" t="n">
         <v>12</v>
@@ -4442,10 +4509,10 @@
         <v>4</v>
       </c>
       <c r="AY22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA22" t="n">
         <v>6</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-27-2010-11</t>
+          <t>2011-03-27</t>
         </is>
       </c>
     </row>
@@ -4483,28 +4550,28 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E23" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F23" t="n">
         <v>26</v>
       </c>
       <c r="G23" t="n">
-        <v>0.639</v>
+        <v>0.644</v>
       </c>
       <c r="H23" t="n">
         <v>48.3</v>
       </c>
       <c r="I23" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J23" t="n">
         <v>78.5</v>
       </c>
       <c r="K23" t="n">
-        <v>0.461</v>
+        <v>0.463</v>
       </c>
       <c r="L23" t="n">
         <v>9.4</v>
@@ -4519,31 +4586,31 @@
         <v>17.7</v>
       </c>
       <c r="P23" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R23" t="n">
         <v>10.5</v>
       </c>
       <c r="S23" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="T23" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="U23" t="n">
         <v>20.1</v>
       </c>
       <c r="V23" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W23" t="n">
         <v>6.5</v>
       </c>
       <c r="X23" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y23" t="n">
         <v>3.9</v>
@@ -4552,19 +4619,19 @@
         <v>20.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AB23" t="n">
-        <v>99.59999999999999</v>
+        <v>99.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AE23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF23" t="n">
         <v>8</v>
@@ -4582,7 +4649,7 @@
         <v>25</v>
       </c>
       <c r="AK23" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AL23" t="n">
         <v>1</v>
@@ -4594,10 +4661,10 @@
         <v>9</v>
       </c>
       <c r="AO23" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AP23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ23" t="n">
         <v>30</v>
@@ -4606,7 +4673,7 @@
         <v>20</v>
       </c>
       <c r="AS23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AT23" t="n">
         <v>6</v>
@@ -4615,10 +4682,10 @@
         <v>25</v>
       </c>
       <c r="AV23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX23" t="n">
         <v>17</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-27-2010-11</t>
+          <t>2011-03-27</t>
         </is>
       </c>
     </row>
@@ -4680,10 +4747,10 @@
         <v>48.6</v>
       </c>
       <c r="I24" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="J24" t="n">
-        <v>82.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="K24" t="n">
         <v>0.462</v>
@@ -4692,16 +4759,16 @@
         <v>5.5</v>
       </c>
       <c r="M24" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="N24" t="n">
         <v>0.361</v>
       </c>
       <c r="O24" t="n">
-        <v>17.9</v>
+        <v>17.6</v>
       </c>
       <c r="P24" t="n">
-        <v>23.2</v>
+        <v>22.8</v>
       </c>
       <c r="Q24" t="n">
         <v>0.771</v>
@@ -4719,31 +4786,31 @@
         <v>22.6</v>
       </c>
       <c r="V24" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="W24" t="n">
         <v>7.5</v>
       </c>
       <c r="X24" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z24" t="n">
         <v>19.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>99.59999999999999</v>
+        <v>99.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AE24" t="n">
         <v>15</v>
@@ -4755,16 +4822,16 @@
         <v>15</v>
       </c>
       <c r="AH24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI24" t="n">
         <v>10</v>
       </c>
       <c r="AJ24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK24" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AL24" t="n">
         <v>22</v>
@@ -4773,16 +4840,16 @@
         <v>23</v>
       </c>
       <c r="AN24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO24" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AP24" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AQ24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR24" t="n">
         <v>21</v>
@@ -4794,19 +4861,19 @@
         <v>10</v>
       </c>
       <c r="AU24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW24" t="n">
         <v>8</v>
       </c>
       <c r="AX24" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AY24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ24" t="n">
         <v>6</v>
@@ -4815,10 +4882,10 @@
         <v>27</v>
       </c>
       <c r="BB24" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BC24" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-27-2010-11</t>
+          <t>2011-03-27</t>
         </is>
       </c>
     </row>
@@ -4847,88 +4914,88 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E25" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F25" t="n">
         <v>35</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5</v>
+        <v>0.507</v>
       </c>
       <c r="H25" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="I25" t="n">
         <v>39.2</v>
       </c>
       <c r="J25" t="n">
-        <v>83.5</v>
+        <v>83.3</v>
       </c>
       <c r="K25" t="n">
-        <v>0.469</v>
+        <v>0.47</v>
       </c>
       <c r="L25" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="M25" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="N25" t="n">
-        <v>0.38</v>
+        <v>0.385</v>
       </c>
       <c r="O25" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="P25" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.762</v>
+        <v>0.764</v>
       </c>
       <c r="R25" t="n">
         <v>10</v>
       </c>
       <c r="S25" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T25" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="U25" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="V25" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W25" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="X25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y25" t="n">
         <v>4.4</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>4.3</v>
       </c>
       <c r="Z25" t="n">
         <v>20.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>105.1</v>
+        <v>105.3</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AE25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF25" t="n">
         <v>15</v>
@@ -4955,46 +5022,46 @@
         <v>3</v>
       </c>
       <c r="AN25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ25" t="n">
         <v>17</v>
       </c>
       <c r="AR25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS25" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AT25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ25" t="n">
         <v>13</v>
       </c>
       <c r="BA25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BB25" t="n">
         <v>4</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-27-2010-11</t>
+          <t>2011-03-27</t>
         </is>
       </c>
     </row>
@@ -5029,88 +5096,88 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E26" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F26" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.583</v>
       </c>
       <c r="H26" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>36</v>
+        <v>36.2</v>
       </c>
       <c r="J26" t="n">
-        <v>80.59999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K26" t="n">
         <v>0.447</v>
       </c>
       <c r="L26" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="M26" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="N26" t="n">
-        <v>0.34</v>
+        <v>0.344</v>
       </c>
       <c r="O26" t="n">
-        <v>18</v>
+        <v>17.8</v>
       </c>
       <c r="P26" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="Q26" t="n">
         <v>0.8</v>
       </c>
       <c r="R26" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="S26" t="n">
-        <v>27</v>
+        <v>27.1</v>
       </c>
       <c r="T26" t="n">
-        <v>39.1</v>
+        <v>39.4</v>
       </c>
       <c r="U26" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="V26" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="W26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X26" t="n">
         <v>4.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z26" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>96.2</v>
+        <v>96.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AE26" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AF26" t="n">
         <v>10</v>
@@ -5125,37 +5192,37 @@
         <v>25</v>
       </c>
       <c r="AJ26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL26" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AM26" t="n">
         <v>12</v>
       </c>
       <c r="AN26" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AO26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AP26" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ26" t="n">
         <v>3</v>
       </c>
       <c r="AR26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AS26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU26" t="n">
         <v>16</v>
@@ -5176,13 +5243,13 @@
         <v>5</v>
       </c>
       <c r="BA26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-27-2010-11</t>
+          <t>2011-03-27</t>
         </is>
       </c>
     </row>
@@ -5235,61 +5302,61 @@
         <v>0.448</v>
       </c>
       <c r="L27" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="M27" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.346</v>
+        <v>0.343</v>
       </c>
       <c r="O27" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="P27" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.732</v>
+        <v>0.731</v>
       </c>
       <c r="R27" t="n">
         <v>13.2</v>
       </c>
       <c r="S27" t="n">
-        <v>30.6</v>
+        <v>30.4</v>
       </c>
       <c r="T27" t="n">
-        <v>43.8</v>
+        <v>43.6</v>
       </c>
       <c r="U27" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V27" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="W27" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X27" t="n">
         <v>4.9</v>
       </c>
       <c r="Y27" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>98.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC27" t="n">
-        <v>-5.3</v>
+        <v>-5.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AE27" t="n">
         <v>27</v>
@@ -5301,7 +5368,7 @@
         <v>27</v>
       </c>
       <c r="AH27" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AI27" t="n">
         <v>11</v>
@@ -5316,25 +5383,25 @@
         <v>25</v>
       </c>
       <c r="AM27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AN27" t="n">
         <v>24</v>
       </c>
-      <c r="AN27" t="n">
-        <v>22</v>
-      </c>
       <c r="AO27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP27" t="n">
         <v>16</v>
       </c>
       <c r="AQ27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR27" t="n">
         <v>2</v>
       </c>
       <c r="AS27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AT27" t="n">
         <v>5</v>
@@ -5358,7 +5425,7 @@
         <v>25</v>
       </c>
       <c r="BA27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BB27" t="n">
         <v>19</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-27-2010-11</t>
+          <t>2011-03-27</t>
         </is>
       </c>
     </row>
@@ -5396,22 +5463,22 @@
         <v>72</v>
       </c>
       <c r="E28" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G28" t="n">
-        <v>0.778</v>
+        <v>0.792</v>
       </c>
       <c r="H28" t="n">
         <v>48.2</v>
       </c>
       <c r="I28" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="J28" t="n">
-        <v>80.7</v>
+        <v>80.8</v>
       </c>
       <c r="K28" t="n">
         <v>0.474</v>
@@ -5423,55 +5490,55 @@
         <v>21</v>
       </c>
       <c r="N28" t="n">
-        <v>0.401</v>
+        <v>0.402</v>
       </c>
       <c r="O28" t="n">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
       <c r="P28" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.769</v>
+        <v>0.77</v>
       </c>
       <c r="R28" t="n">
         <v>10</v>
       </c>
       <c r="S28" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T28" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="U28" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="V28" t="n">
         <v>13.6</v>
       </c>
       <c r="W28" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X28" t="n">
         <v>4.7</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="AA28" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>103.3</v>
+        <v>103.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5486,10 +5553,10 @@
         <v>25</v>
       </c>
       <c r="AI28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AJ28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK28" t="n">
         <v>5</v>
@@ -5510,25 +5577,25 @@
         <v>15</v>
       </c>
       <c r="AQ28" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AR28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT28" t="n">
         <v>12</v>
       </c>
       <c r="AU28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV28" t="n">
         <v>8</v>
       </c>
       <c r="AW28" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AX28" t="n">
         <v>19</v>
@@ -5540,13 +5607,13 @@
         <v>1</v>
       </c>
       <c r="BA28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB28" t="n">
         <v>6</v>
       </c>
       <c r="BC28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-27-2010-11</t>
+          <t>2011-03-27</t>
         </is>
       </c>
     </row>
@@ -5575,28 +5642,28 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E29" t="n">
         <v>20</v>
       </c>
       <c r="F29" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G29" t="n">
-        <v>0.278</v>
+        <v>0.274</v>
       </c>
       <c r="H29" t="n">
         <v>48.3</v>
       </c>
       <c r="I29" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="J29" t="n">
-        <v>82.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>0.466</v>
+        <v>0.465</v>
       </c>
       <c r="L29" t="n">
         <v>4.3</v>
@@ -5623,10 +5690,10 @@
         <v>28.6</v>
       </c>
       <c r="T29" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="U29" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V29" t="n">
         <v>14.7</v>
@@ -5638,28 +5705,28 @@
         <v>4.3</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Z29" t="n">
         <v>22.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AB29" t="n">
-        <v>99.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="AC29" t="n">
         <v>-6.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AE29" t="n">
         <v>26</v>
       </c>
       <c r="AF29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG29" t="n">
         <v>26</v>
@@ -5671,7 +5738,7 @@
         <v>4</v>
       </c>
       <c r="AJ29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK29" t="n">
         <v>10</v>
@@ -5686,16 +5753,16 @@
         <v>30</v>
       </c>
       <c r="AO29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP29" t="n">
         <v>18</v>
       </c>
       <c r="AQ29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AR29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AS29" t="n">
         <v>27</v>
@@ -5710,16 +5777,16 @@
         <v>22</v>
       </c>
       <c r="AW29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX29" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AY29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA29" t="n">
         <v>26</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-27-2010-11</t>
+          <t>2011-03-27</t>
         </is>
       </c>
     </row>
@@ -5757,61 +5824,61 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E30" t="n">
         <v>36</v>
       </c>
       <c r="F30" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5</v>
+        <v>0.486</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
       </c>
       <c r="I30" t="n">
-        <v>37.6</v>
+        <v>37.4</v>
       </c>
       <c r="J30" t="n">
-        <v>80.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.467</v>
+        <v>0.465</v>
       </c>
       <c r="L30" t="n">
         <v>5.3</v>
       </c>
       <c r="M30" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="N30" t="n">
-        <v>0.348</v>
+        <v>0.345</v>
       </c>
       <c r="O30" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="P30" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.78</v>
+        <v>0.777</v>
       </c>
       <c r="R30" t="n">
         <v>10.8</v>
       </c>
       <c r="S30" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="T30" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="U30" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="V30" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W30" t="n">
         <v>7.7</v>
@@ -5823,19 +5890,19 @@
         <v>5</v>
       </c>
       <c r="Z30" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="AA30" t="n">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>100.3</v>
+        <v>100.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>-1.2</v>
+        <v>-1.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AE30" t="n">
         <v>16</v>
@@ -5844,16 +5911,16 @@
         <v>17</v>
       </c>
       <c r="AG30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH30" t="n">
         <v>8</v>
       </c>
       <c r="AI30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ30" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AK30" t="n">
         <v>8</v>
@@ -5865,7 +5932,7 @@
         <v>22</v>
       </c>
       <c r="AN30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO30" t="n">
         <v>6</v>
@@ -5874,28 +5941,28 @@
         <v>7</v>
       </c>
       <c r="AQ30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS30" t="n">
         <v>28</v>
       </c>
       <c r="AT30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW30" t="n">
         <v>7</v>
       </c>
       <c r="AX30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY30" t="n">
         <v>20</v>
@@ -5904,13 +5971,13 @@
         <v>30</v>
       </c>
       <c r="BA30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-27-2010-11</t>
+          <t>2011-03-27</t>
         </is>
       </c>
     </row>
@@ -5954,10 +6021,10 @@
         <v>48.6</v>
       </c>
       <c r="I31" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J31" t="n">
-        <v>83.90000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="K31" t="n">
         <v>0.441</v>
@@ -5966,10 +6033,10 @@
         <v>4.9</v>
       </c>
       <c r="M31" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="N31" t="n">
-        <v>0.332</v>
+        <v>0.331</v>
       </c>
       <c r="O31" t="n">
         <v>17.7</v>
@@ -5978,19 +6045,19 @@
         <v>23.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.75</v>
+        <v>0.747</v>
       </c>
       <c r="R31" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="S31" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="T31" t="n">
-        <v>41</v>
+        <v>40.7</v>
       </c>
       <c r="U31" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="V31" t="n">
         <v>15.4</v>
@@ -5999,25 +6066,25 @@
         <v>7.9</v>
       </c>
       <c r="X31" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="AA31" t="n">
         <v>20.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>96.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>-8</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="AD31" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
@@ -6029,10 +6096,10 @@
         <v>28</v>
       </c>
       <c r="AH31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ31" t="n">
         <v>5</v>
@@ -6050,28 +6117,28 @@
         <v>27</v>
       </c>
       <c r="AO31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ31" t="n">
         <v>24</v>
       </c>
       <c r="AR31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AS31" t="n">
         <v>25</v>
       </c>
       <c r="AT31" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AU31" t="n">
         <v>27</v>
       </c>
       <c r="AV31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW31" t="n">
         <v>6</v>
@@ -6080,7 +6147,7 @@
         <v>1</v>
       </c>
       <c r="AY31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ31" t="n">
         <v>29</v>
@@ -6089,7 +6156,7 @@
         <v>23</v>
       </c>
       <c r="BB31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC31" t="n">
         <v>29</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-27-2010-11</t>
+          <t>2011-03-27</t>
         </is>
       </c>
     </row>
